--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>520395.59</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>482902.5</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>423026.22</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>418511.34</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>411350.25</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>410831.56</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>400249.06</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>395510.72</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>380869.97</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>371290.97</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>360401.28</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>356060.62</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>355284.59</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>349343.72</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>342989.03</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>341806.69</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>340710.47</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>339556.66</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>325759.16</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>317374.44</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -656,9 +591,6 @@
       <c r="B22">
         <v>312231.62</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -669,9 +601,6 @@
       <c r="B23">
         <v>311431.03</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +611,6 @@
       <c r="B24">
         <v>305766.16</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -695,9 +621,6 @@
       <c r="B25">
         <v>304418.31</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -708,9 +631,6 @@
       <c r="B26">
         <v>296987.66</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -721,9 +641,6 @@
       <c r="B27">
         <v>294221.09</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -734,9 +651,6 @@
       <c r="B28">
         <v>284590.38</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,9 +661,6 @@
       <c r="B29">
         <v>281918.34</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -760,9 +671,6 @@
       <c r="B30">
         <v>280747.75</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -773,9 +681,6 @@
       <c r="B31">
         <v>274392.75</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -786,9 +691,6 @@
       <c r="B32">
         <v>264802.12</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -799,9 +701,6 @@
       <c r="B33">
         <v>261125.3</v>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -812,9 +711,6 @@
       <c r="B34">
         <v>253305.25</v>
       </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -825,9 +721,6 @@
       <c r="B35">
         <v>251931.5</v>
       </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -838,9 +731,6 @@
       <c r="B36">
         <v>248963.61</v>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -851,9 +741,6 @@
       <c r="B37">
         <v>196306.73</v>
       </c>
-      <c r="F37" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -864,9 +751,6 @@
       <c r="B38">
         <v>194174.95</v>
       </c>
-      <c r="F38" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -876,9 +760,6 @@
       </c>
       <c r="B39">
         <v>191960.28</v>
-      </c>
-      <c r="F39" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>520395.59</v>
       </c>
+      <c r="C2">
+        <v>444546.66</v>
+      </c>
+      <c r="D2">
+        <v>75848.93000000005</v>
+      </c>
+      <c r="E2">
+        <v>17.06208522632924</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>482902.5</v>
       </c>
+      <c r="C3">
+        <v>422421.84</v>
+      </c>
+      <c r="D3">
+        <v>60480.65999999997</v>
+      </c>
+      <c r="E3">
+        <v>14.31759778329642</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>423026.22</v>
       </c>
+      <c r="C4">
+        <v>354340.81</v>
+      </c>
+      <c r="D4">
+        <v>68685.40999999997</v>
+      </c>
+      <c r="E4">
+        <v>19.38399644116633</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -431,6 +458,15 @@
       <c r="B6">
         <v>411350.25</v>
       </c>
+      <c r="C6">
+        <v>356730.06</v>
+      </c>
+      <c r="D6">
+        <v>54620.19</v>
+      </c>
+      <c r="E6">
+        <v>15.31135054892767</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -441,6 +477,15 @@
       <c r="B7">
         <v>410831.56</v>
       </c>
+      <c r="C7">
+        <v>329371.28</v>
+      </c>
+      <c r="D7">
+        <v>81460.27999999997</v>
+      </c>
+      <c r="E7">
+        <v>24.73205314075957</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -451,6 +496,15 @@
       <c r="B8">
         <v>400249.06</v>
       </c>
+      <c r="C8">
+        <v>336821.06</v>
+      </c>
+      <c r="D8">
+        <v>63428</v>
+      </c>
+      <c r="E8">
+        <v>18.83136404831694</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -461,6 +515,15 @@
       <c r="B9">
         <v>395510.72</v>
       </c>
+      <c r="C9">
+        <v>323399.44</v>
+      </c>
+      <c r="D9">
+        <v>72111.27999999997</v>
+      </c>
+      <c r="E9">
+        <v>22.29789884608333</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -471,6 +534,15 @@
       <c r="B10">
         <v>380869.97</v>
       </c>
+      <c r="C10">
+        <v>329780.44</v>
+      </c>
+      <c r="D10">
+        <v>51089.52999999997</v>
+      </c>
+      <c r="E10">
+        <v>15.49198309032518</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -491,6 +563,15 @@
       <c r="B12">
         <v>360401.28</v>
       </c>
+      <c r="C12">
+        <v>298289.5</v>
+      </c>
+      <c r="D12">
+        <v>62111.78000000003</v>
+      </c>
+      <c r="E12">
+        <v>20.82265047881338</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -501,6 +582,15 @@
       <c r="B13">
         <v>356060.62</v>
       </c>
+      <c r="C13">
+        <v>249985.77</v>
+      </c>
+      <c r="D13">
+        <v>106074.85</v>
+      </c>
+      <c r="E13">
+        <v>42.43235524966082</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -511,6 +601,15 @@
       <c r="B14">
         <v>355284.59</v>
       </c>
+      <c r="C14">
+        <v>307048.56</v>
+      </c>
+      <c r="D14">
+        <v>48236.03000000003</v>
+      </c>
+      <c r="E14">
+        <v>15.70957701283473</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -521,245 +620,489 @@
       <c r="B15">
         <v>349343.72</v>
       </c>
+      <c r="C15">
+        <v>297544.66</v>
+      </c>
+      <c r="D15">
+        <v>51799.06</v>
+      </c>
+      <c r="E15">
+        <v>17.40883536609261</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Panquehue</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B16">
-        <v>342989.03</v>
+        <v>344618.94</v>
+      </c>
+      <c r="C16">
+        <v>293677.31</v>
+      </c>
+      <c r="D16">
+        <v>50941.63</v>
+      </c>
+      <c r="E16">
+        <v>17.34612387998242</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Panquehue</t>
         </is>
       </c>
       <c r="B17">
-        <v>341806.69</v>
+        <v>342989.03</v>
+      </c>
+      <c r="C17">
+        <v>258214.5</v>
+      </c>
+      <c r="D17">
+        <v>84774.53000000003</v>
+      </c>
+      <c r="E17">
+        <v>32.83104937948877</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="B18">
-        <v>340710.47</v>
+        <v>341806.69</v>
+      </c>
+      <c r="C18">
+        <v>291824.12</v>
+      </c>
+      <c r="D18">
+        <v>49982.57000000001</v>
+      </c>
+      <c r="E18">
+        <v>17.12763496040013</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="B19">
-        <v>339556.66</v>
+        <v>340710.47</v>
+      </c>
+      <c r="C19">
+        <v>284980.78</v>
+      </c>
+      <c r="D19">
+        <v>55729.68999999994</v>
+      </c>
+      <c r="E19">
+        <v>19.55559599492989</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="B20">
-        <v>325759.16</v>
+        <v>339556.66</v>
+      </c>
+      <c r="C20">
+        <v>287839.53</v>
+      </c>
+      <c r="D20">
+        <v>51717.12999999995</v>
+      </c>
+      <c r="E20">
+        <v>17.96734798726218</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Catemu</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B21">
-        <v>317374.44</v>
+        <v>325759.16</v>
+      </c>
+      <c r="C21">
+        <v>277329.66</v>
+      </c>
+      <c r="D21">
+        <v>48429.5</v>
+      </c>
+      <c r="E21">
+        <v>17.46279139418409</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Isla de Pascua</t>
+          <t>Catemu</t>
         </is>
       </c>
       <c r="B22">
-        <v>312231.62</v>
+        <v>317374.44</v>
+      </c>
+      <c r="C22">
+        <v>269994.12</v>
+      </c>
+      <c r="D22">
+        <v>47380.32000000001</v>
+      </c>
+      <c r="E22">
+        <v>17.54864883724134</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>Isla de Pascua</t>
         </is>
       </c>
       <c r="B23">
-        <v>311431.03</v>
+        <v>312231.62</v>
+      </c>
+      <c r="C23">
+        <v>275952.97</v>
+      </c>
+      <c r="D23">
+        <v>36278.65000000002</v>
+      </c>
+      <c r="E23">
+        <v>13.14667858077412</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="B24">
-        <v>305766.16</v>
+        <v>311431.03</v>
+      </c>
+      <c r="C24">
+        <v>260976.92</v>
+      </c>
+      <c r="D24">
+        <v>50454.11000000002</v>
+      </c>
+      <c r="E24">
+        <v>19.33278620960046</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="B25">
-        <v>304418.31</v>
+        <v>305766.16</v>
+      </c>
+      <c r="C25">
+        <v>264067.91</v>
+      </c>
+      <c r="D25">
+        <v>41698.25</v>
+      </c>
+      <c r="E25">
+        <v>15.79072974069435</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="B26">
-        <v>296987.66</v>
+        <v>304418.31</v>
+      </c>
+      <c r="C26">
+        <v>259080.61</v>
+      </c>
+      <c r="D26">
+        <v>45337.70000000001</v>
+      </c>
+      <c r="E26">
+        <v>17.49945702227582</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="B27">
-        <v>294221.09</v>
+        <v>296987.66</v>
+      </c>
+      <c r="C27">
+        <v>256245.44</v>
+      </c>
+      <c r="D27">
+        <v>40742.21999999997</v>
+      </c>
+      <c r="E27">
+        <v>15.89968586367818</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Santa María</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="B28">
-        <v>284590.38</v>
+        <v>294221.09</v>
+      </c>
+      <c r="C28">
+        <v>252268.94</v>
+      </c>
+      <c r="D28">
+        <v>41952.15000000002</v>
+      </c>
+      <c r="E28">
+        <v>16.62993073978907</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Puchuncaví</t>
+          <t>Santa María</t>
         </is>
       </c>
       <c r="B29">
-        <v>281918.34</v>
+        <v>284590.38</v>
+      </c>
+      <c r="C29">
+        <v>236915.11</v>
+      </c>
+      <c r="D29">
+        <v>47675.27000000002</v>
+      </c>
+      <c r="E29">
+        <v>20.12335557660296</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
+          <t>Puchuncaví</t>
         </is>
       </c>
       <c r="B30">
-        <v>280747.75</v>
+        <v>281918.34</v>
+      </c>
+      <c r="C30">
+        <v>225798.11</v>
+      </c>
+      <c r="D30">
+        <v>56120.23000000004</v>
+      </c>
+      <c r="E30">
+        <v>24.85416286256783</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Papudo</t>
+          <t>Algarrobo</t>
         </is>
       </c>
       <c r="B31">
-        <v>274392.75</v>
+        <v>280747.75</v>
+      </c>
+      <c r="C31">
+        <v>222848.97</v>
+      </c>
+      <c r="D31">
+        <v>57898.78</v>
+      </c>
+      <c r="E31">
+        <v>25.98117460448661</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>Papudo</t>
         </is>
       </c>
       <c r="B32">
-        <v>264802.12</v>
+        <v>274392.75</v>
+      </c>
+      <c r="C32">
+        <v>225196.42</v>
+      </c>
+      <c r="D32">
+        <v>49196.32999999999</v>
+      </c>
+      <c r="E32">
+        <v>21.84596451400069</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Petorca</t>
+          <t>La Ligua</t>
         </is>
       </c>
       <c r="B33">
-        <v>261125.3</v>
+        <v>264802.12</v>
+      </c>
+      <c r="C33">
+        <v>228452.78</v>
+      </c>
+      <c r="D33">
+        <v>36349.34</v>
+      </c>
+      <c r="E33">
+        <v>15.91109550078576</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Putaendo</t>
+          <t>Petorca</t>
         </is>
       </c>
       <c r="B34">
-        <v>253305.25</v>
+        <v>261125.3</v>
+      </c>
+      <c r="C34">
+        <v>224251.38</v>
+      </c>
+      <c r="D34">
+        <v>36873.91999999998</v>
+      </c>
+      <c r="E34">
+        <v>16.44311843253763</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Juan Fernandez</t>
+          <t>Putaendo</t>
         </is>
       </c>
       <c r="B35">
-        <v>251931.5</v>
+        <v>253305.25</v>
+      </c>
+      <c r="C35">
+        <v>208825.89</v>
+      </c>
+      <c r="D35">
+        <v>44479.35999999999</v>
+      </c>
+      <c r="E35">
+        <v>21.2997344342696</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Olmué</t>
+          <t>Juan Fernández</t>
         </is>
       </c>
       <c r="B36">
-        <v>248963.61</v>
+        <v>251931.5</v>
+      </c>
+      <c r="C36">
+        <v>202444.09</v>
+      </c>
+      <c r="D36">
+        <v>49487.41</v>
+      </c>
+      <c r="E36">
+        <v>24.44497638829566</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Olmué</t>
         </is>
       </c>
       <c r="B37">
-        <v>196306.73</v>
+        <v>248963.61</v>
+      </c>
+      <c r="C37">
+        <v>196751.02</v>
+      </c>
+      <c r="D37">
+        <v>52212.59</v>
+      </c>
+      <c r="E37">
+        <v>26.53739228391294</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>El Quisco</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="B38">
-        <v>194174.95</v>
+        <v>196306.73</v>
+      </c>
+      <c r="C38">
+        <v>165060.06</v>
+      </c>
+      <c r="D38">
+        <v>31246.67000000001</v>
+      </c>
+      <c r="E38">
+        <v>18.93048506101356</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>El Quisco</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>194174.95</v>
+      </c>
+      <c r="C39">
+        <v>163021.22</v>
+      </c>
+      <c r="D39">
+        <v>31153.73000000001</v>
+      </c>
+      <c r="E39">
+        <v>19.11022994429805</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>El Tabo</t>
         </is>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>191960.28</v>
+      </c>
+      <c r="C40">
+        <v>163241.67</v>
+      </c>
+      <c r="D40">
+        <v>28718.60999999999</v>
+      </c>
+      <c r="E40">
+        <v>17.59269554152441</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
@@ -1112,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1121,20 +1121,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>280747.75</v>
+          <t>Rinconada</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1143,48 +1135,33 @@
           <t>Cabildo</t>
         </is>
       </c>
-      <c r="B3">
-        <v>311431.03</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Calera</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>371290.97</v>
+          <t>Petorca</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>400249.06</v>
+          <t>Panquehue</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cartagena</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>196306.73</v>
+          <t>Olmué</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Casablanca</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>340710.47</v>
+          <t>Cartagena</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1193,148 +1170,103 @@
           <t>Catemu</t>
         </is>
       </c>
-      <c r="B8">
-        <v>317374.44</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Concón</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>520395.59</v>
+          <t>Llaillay</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El Quisco</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>194174.95</v>
+          <t>San Felipe</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El Tabo</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>191960.28</v>
+          <t>Santa María</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>294221.09</v>
+          <t>Villa Alemana</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>La Cruz</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>482902.5</v>
+          <t>Santo Domingo</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>La Ligua</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>264802.12</v>
+          <t>San Antonio</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Limache</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>304418.31</v>
+          <t>El Tabo</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Llaillay</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>418511.34</v>
+          <t>El Quisco</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Los Andes</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>423026.22</v>
+          <t>Algarrobo</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nogales</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>360401.28</v>
+          <t>Casablanca</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Olmué</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>248963.61</v>
+          <t>Valparaíso</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Panquehue</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>342989.03</v>
+          <t>Viña del Mar</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Papudo</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>274392.75</v>
+          <t>Concón</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Petorca</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>261125.3</v>
+          <t>Quintero</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1343,148 +1275,103 @@
           <t>Puchuncaví</t>
         </is>
       </c>
-      <c r="B23">
-        <v>281918.34</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Putaendo</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>253305.25</v>
+          <t>Zapallar</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quillota</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>339556.66</v>
+          <t>Papudo</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Quilpué</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>355284.59</v>
+          <t>La Ligua</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quintero</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>296987.66</v>
+          <t>Limache</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rinconada</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>410831.56</v>
+          <t>Quillota</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>305766.16</v>
+          <t>Calera</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>San Esteban</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>395510.72</v>
+          <t>Nogales</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Felipe</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>341806.69</v>
+          <t>Calle Larga</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Santa María</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>284590.38</v>
+          <t>La Cruz</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>411350.25</v>
+          <t>Putaendo</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>325759.16</v>
+          <t>San Esteban</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>349343.72</v>
+          <t>Los Andes</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>380869.97</v>
+          <t>Hijuelas</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zapallar</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>356060.62</v>
+          <t>Quilpué</t>
+        </is>
       </c>
     </row>
   </sheetData>
